--- a/plants_data/CO2_Pipeline.xlsx
+++ b/plants_data/CO2_Pipeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355540A7-A3B5-48E2-8EE6-C14823D37B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7F6CDB-915D-475D-8EC8-8D0B493D52B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="2" r:id="rId1"/>

--- a/plants_data/CO2_Pipeline.xlsx
+++ b/plants_data/CO2_Pipeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17F6B48-DDBA-4D2E-A2B5-5530522B0927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E7EFDF-8F5C-49EE-B8B1-579E67219DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="5" r:id="rId1"/>
@@ -427,19 +427,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="D2">
-        <v>186.8</v>
+        <v>187</v>
       </c>
       <c r="E2">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>287.5</v>
+        <v>288</v>
       </c>
       <c r="G2">
-        <v>112.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -447,22 +447,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>232.7</v>
+        <v>233</v>
       </c>
       <c r="E3">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="F3">
-        <v>382.8</v>
+        <v>383</v>
       </c>
       <c r="G3">
-        <v>150.19999999999999</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -470,22 +470,22 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>186.8</v>
+        <v>187</v>
       </c>
       <c r="C4">
-        <v>232.7</v>
+        <v>233</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>200.3</v>
+        <v>200</v>
       </c>
       <c r="F4">
-        <v>244.4</v>
+        <v>244</v>
       </c>
       <c r="G4">
-        <v>82.9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -493,22 +493,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="D5">
-        <v>200.3</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>275.10000000000002</v>
+        <v>275</v>
       </c>
       <c r="G5">
-        <v>131.1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -516,22 +516,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>287.5</v>
+        <v>288</v>
       </c>
       <c r="C6">
-        <v>382.8</v>
+        <v>383</v>
       </c>
       <c r="D6">
-        <v>244.4</v>
+        <v>244</v>
       </c>
       <c r="E6">
-        <v>275.10000000000002</v>
+        <v>275</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>273.8</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -539,19 +539,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>112.2</v>
+        <v>112</v>
       </c>
       <c r="C7">
-        <v>150.19999999999999</v>
+        <v>150</v>
       </c>
       <c r="D7">
-        <v>82.9</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>131.1</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>273.8</v>
+        <v>274</v>
       </c>
       <c r="G7">
         <v>0</v>
